--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Re8978b4f8e29430d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R651b3c50cdc249f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R63cc2dafe5cf49d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R9baa990ea81f41f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R784df6aa788540c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Ra05b575b1f26445b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rc30e3c175b7347ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R987fd6b3b5e84d00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R9a8b6be465774434"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Re08f5b6c70b94921"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -361,7 +361,7 @@
         <x:v>CSV</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>运营人员复核申请去向</x:v>
+        <x:v>运营人员跟进申请去向</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
@@ -375,7 +375,7 @@
         <x:v>JSON</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>变更负责人决定是否进入导入复核</x:v>
+        <x:v>发布负责人安排导入</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -432,7 +432,7 @@
         <x:v>rejected|unsupported_host</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>申请的landing_url或requested_slug与migration_policy.json公开规则</x:v>
+        <x:v>申请的landing_url或requested_slug与migration_policy.json规则</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
@@ -446,7 +446,7 @@
         <x:v>rejected|invalid_slug</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>申请的landing_url或requested_slug与migration_policy.json公开规则</x:v>
+        <x:v>申请的landing_url或requested_slug与migration_policy.json规则</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
@@ -460,7 +460,7 @@
         <x:v>rejected|non_https_scheme</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>申请的landing_url或requested_slug与migration_policy.json公开规则</x:v>
+        <x:v>申请的landing_url或requested_slug与migration_policy.json规则</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -531,7 +531,7 @@
         <x:v>按request_id比较映射</x:v>
       </x:c>
       <x:c r="D4" s="7" t="str">
-        <x:v>三份输入按申请顺序、短码合同及占用规则推导</x:v>
+        <x:v>三份输入按申请顺序、短码政策及占用状态推导</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="96" customHeight="1">
@@ -545,7 +545,7 @@
         <x:v>按request_id比较映射</x:v>
       </x:c>
       <x:c r="D5" s="7" t="str">
-        <x:v>申请地址、短码、运行时刻及现网快照推导</x:v>
+        <x:v>申请地址、短码、处理时刻及现网快照推导</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -642,7 +642,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F4" s="7" t="str">
-        <x:v>output/transition_log.csv按resolution复算rejected_count</x:v>
+        <x:v>output/transition_log.csv按resolution分类计数rejected_count</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="32" customHeight="1">
@@ -662,7 +662,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="7" t="str">
-        <x:v>output/transition_log.csv按resolution复算reused_count</x:v>
+        <x:v>output/transition_log.csv按resolution分类计数reused_count</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
@@ -682,7 +682,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="7" t="str">
-        <x:v>output/transition_log.csv按resolution复算reclaimed_count</x:v>
+        <x:v>output/transition_log.csv按resolution分类计数reclaimed_count</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="46" customHeight="1">
@@ -702,7 +702,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="7" t="str">
-        <x:v>output/transition_log.csv按resolution复算collision_allocated_count</x:v>
+        <x:v>output/transition_log.csv按resolution分类计数collision_allocated_count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -738,7 +738,7 @@
         <x:v>函数拆分、内部容器和临时变量可以不同</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Node.js真实执行且业务字段一致</x:v>
+        <x:v>Node.js处理后的业务字段一致</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
@@ -771,7 +771,7 @@
         <x:v>Node.js可执行文件路径与解压目录可以不同</x:v>
       </x:c>
       <x:c r="C5" s="7" t="str">
-        <x:v>不依赖WSL、容器或作者绝对路径</x:v>
+        <x:v>相对路径和业务结果不变</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="32" customHeight="1">
@@ -782,7 +782,7 @@
         <x:v>源码注释可以不同</x:v>
       </x:c>
       <x:c r="C6" s="7" t="str">
-        <x:v>不得改变政策、地址或短码裁决</x:v>
+        <x:v>不改变政策、地址或短码处置</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Ra05b575b1f26445b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rc30e3c175b7347ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R987fd6b3b5e84d00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R9a8b6be465774434"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Re08f5b6c70b94921"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R9163e812f3f54386"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R4f9914d20f034d3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Redbb663f38214435"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rdc2ac808c41e4c2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rdb369e5f22e54650"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R9163e812f3f54386"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R4f9914d20f034d3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Redbb663f38214435"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rdc2ac808c41e4c2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rdb369e5f22e54650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R32bc7bbea64740de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R7bb63911449747c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R9a438270a6bf46c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rfe85b1ba38534dcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R1f743bda496d4768"/>
   </x:sheets>
 </x:workbook>
 </file>
